--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 DEER BUCK GENERAL SEASON - PRIVATE LAND ONLY MUZZLELOADER.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 DEER BUCK GENERAL SEASON - PRIVATE LAND ONLY MUZZLELOADER.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -577,10 +577,15 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Average Age Harvested (previous hunting season)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Avg Days Hunted (previous hunting season)</t>
         </is>
@@ -633,7 +638,8 @@
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr"/>
     </row>
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -682,7 +688,8 @@
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -731,7 +738,8 @@
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
     </row>
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -780,7 +788,8 @@
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -829,7 +838,8 @@
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -878,7 +888,8 @@
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
     </row>
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -927,7 +938,8 @@
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr"/>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -976,7 +988,8 @@
       <c r="L9" s="3" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="3" t="inlineStr"/>
-      <c r="O9" s="3" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr"/>
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -1033,7 +1046,8 @@
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -1086,7 +1100,8 @@
       <c r="L11" s="3" t="inlineStr"/>
       <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="3" t="inlineStr"/>
-      <c r="O11" s="3" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -1135,7 +1150,8 @@
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -1192,7 +1208,8 @@
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr"/>
-      <c r="O13" s="3" t="inlineStr">
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -1245,7 +1262,8 @@
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
-      <c r="O14" s="2" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr"/>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -1294,7 +1312,8 @@
       <c r="L15" s="3" t="inlineStr"/>
       <c r="M15" s="3" t="inlineStr"/>
       <c r="N15" s="3" t="inlineStr"/>
-      <c r="O15" s="3" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -1343,7 +1362,8 @@
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -1396,7 +1416,8 @@
       <c r="L17" s="3" t="inlineStr"/>
       <c r="M17" s="3" t="inlineStr"/>
       <c r="N17" s="3" t="inlineStr"/>
-      <c r="O17" s="3" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr"/>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -1445,7 +1466,8 @@
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="2" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr"/>
     </row>
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
@@ -1494,7 +1516,8 @@
       <c r="L19" s="3" t="inlineStr"/>
       <c r="M19" s="3" t="inlineStr"/>
       <c r="N19" s="3" t="inlineStr"/>
-      <c r="O19" s="3" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr"/>
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -1543,7 +1566,8 @@
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
@@ -1592,7 +1616,8 @@
       <c r="L21" s="3" t="inlineStr"/>
       <c r="M21" s="3" t="inlineStr"/>
       <c r="N21" s="3" t="inlineStr"/>
-      <c r="O21" s="3" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" s="3" t="inlineStr"/>
     </row>
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -1649,7 +1674,8 @@
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
@@ -1702,7 +1728,8 @@
       <c r="L23" s="3" t="inlineStr"/>
       <c r="M23" s="3" t="inlineStr"/>
       <c r="N23" s="3" t="inlineStr"/>
-      <c r="O23" s="3" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" s="3" t="inlineStr"/>
     </row>
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -1751,7 +1778,8 @@
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr"/>
-      <c r="O24" s="2" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" s="2" t="inlineStr"/>
     </row>
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
@@ -1800,7 +1828,8 @@
       <c r="L25" s="3" t="inlineStr"/>
       <c r="M25" s="3" t="inlineStr"/>
       <c r="N25" s="3" t="inlineStr"/>
-      <c r="O25" s="3" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" s="3" t="inlineStr"/>
     </row>
     <row r="26" ht="42" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -1849,7 +1878,8 @@
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr"/>
     </row>
     <row r="27" ht="42" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
@@ -1898,7 +1928,8 @@
       <c r="L27" s="3" t="inlineStr"/>
       <c r="M27" s="3" t="inlineStr"/>
       <c r="N27" s="3" t="inlineStr"/>
-      <c r="O27" s="3" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" s="3" t="inlineStr"/>
     </row>
     <row r="28" ht="42" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -1947,7 +1978,8 @@
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr"/>
     </row>
     <row r="29" ht="42" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
@@ -1996,7 +2028,8 @@
       <c r="L29" s="3" t="inlineStr"/>
       <c r="M29" s="3" t="inlineStr"/>
       <c r="N29" s="3" t="inlineStr"/>
-      <c r="O29" s="3" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O29"/>
